--- a/outputs/daily/hr_rankings_2026-08-16.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-16.xlsx
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>54.7</v>
+        <v>55.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1205,7 +1205,7 @@
         <v>56.1</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -1219,39 +1219,35 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1761,24 +1757,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>572233</t>
+          <t>677594</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Julio Rodríguez</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -1791,17 +1787,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1824,26 +1820,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>42.7</v>
+        <v>46.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>41.2</v>
+        <v>22.3</v>
       </c>
       <c r="R5" t="n">
         <v>56.1</v>
       </c>
       <c r="S5" t="n">
-        <v>76.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>21.8</v>
+        <v>34.9</v>
       </c>
       <c r="V5" t="n">
         <v>50</v>
@@ -1861,7 +1857,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1899,12 +1895,12 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1914,12 +1910,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 1 HR</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1929,97 +1925,97 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>43.09</t>
+          <t>44.43</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>90.47</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>101.5695</t>
+          <t>102.6546</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4056</t>
+          <t>0.4692</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.1757</t>
+          <t>0.195</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.3098</t>
+          <t>0.3482</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>74.31</t>
+          <t>76.61</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>43.41</t>
+          <t>67.06</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>38.56</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>26.26</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.2054</t>
+          <t>0.179</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>42.99</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.3814</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.1492</t>
+          <t>0.1297</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2075,24 +2071,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>668227</t>
+          <t>572233</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Randy Arozarena</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -2105,17 +2101,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2124,7 +2120,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>47</v>
+        <v>48.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2138,26 +2134,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>39.7</v>
+        <v>42.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>22.3</v>
+        <v>41.2</v>
       </c>
       <c r="R6" t="n">
         <v>56.1</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>45.5</v>
+        <v>21.8</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -2165,39 +2161,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2217,27 +2209,27 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/21, 1 HR</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2247,97 +2239,97 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>45.49</t>
+          <t>43.09</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>91.09</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>101.0625</t>
+          <t>101.5695</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>0.4056</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1655</t>
+          <t>0.1757</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3403</t>
+          <t>0.3098</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>71.32</t>
+          <t>74.31</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>24.66</t>
+          <t>43.41</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>33.07</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1789</t>
+          <t>0.2054</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>42.99</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.3814</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.1297</t>
+          <t>0.1492</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2393,12 +2385,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>677594</t>
+          <t>668227</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Julio Rodriguez</t>
+          <t>Randy Arozarena</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2423,7 +2415,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2442,7 +2434,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>47</v>
+        <v>48.1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2456,11 +2448,11 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>46.1</v>
+        <v>39.7</v>
       </c>
       <c r="Q7" t="n">
         <v>22.3</v>
@@ -2469,13 +2461,13 @@
         <v>56.1</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>34.9</v>
+        <v>45.5</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -2483,39 +2475,35 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2535,22 +2523,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -2565,67 +2553,67 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>44.43</t>
+          <t>45.49</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>90.47</t>
+          <t>91.09</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>102.6546</t>
+          <t>101.0625</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.4692</t>
+          <t>0.417</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>0.1655</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3482</t>
+          <t>0.3403</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>76.61</t>
+          <t>71.32</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>67.06</t>
+          <t>24.66</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>38.56</t>
+          <t>33.07</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>26.26</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>0.1789</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -2711,24 +2699,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>665161</t>
+          <t>663728</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jeremy Peña</t>
+          <t>Cal Raleigh</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -2741,17 +2729,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2760,7 +2748,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>46.1</v>
+        <v>47</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2774,26 +2762,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>29.3</v>
+        <v>54</v>
       </c>
       <c r="Q8" t="n">
-        <v>41.2</v>
+        <v>21.2</v>
       </c>
       <c r="R8" t="n">
         <v>56.1</v>
       </c>
       <c r="S8" t="n">
-        <v>93.2</v>
+        <v>64.3</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -2811,7 +2799,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -2849,12 +2837,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2864,112 +2852,112 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/31, 0 HR</t>
+          <t>Last 7 games: 2/23, 0 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>88.48</t>
+          <t>89.69</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>99.8917</t>
+          <t>100.7149</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4222</t>
+          <t>0.4161</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1438</t>
+          <t>0.2236</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3333</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>72.23</t>
+          <t>75.06</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>14.27</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>53.38</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1793</t>
+          <t>0.1971</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>42.99</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.3814</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.1492</t>
+          <t>0.1297</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3025,24 +3013,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>670623</t>
+          <t>801126</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Isaac Paredes</t>
+          <t>Brock Rodden</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -3055,17 +3043,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3074,7 +3062,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>45.8</v>
+        <v>46.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3088,26 +3076,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>18.7</v>
+        <v>57.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>41.2</v>
+        <v>21.2</v>
       </c>
       <c r="R9" t="n">
         <v>56.1</v>
       </c>
       <c r="S9" t="n">
-        <v>96.59999999999999</v>
+        <v>44.8</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U9" t="n">
-        <v>53.9</v>
+        <v>19.5</v>
       </c>
       <c r="V9" t="n">
         <v>50</v>
@@ -3125,7 +3113,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -3146,7 +3134,7 @@
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr"/>
@@ -3158,132 +3146,132 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Contact streak: 10/28 over last 7 games</t>
+          <t>Last 2 games: 2/8, 0 HR</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>86.49</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>96.9468</t>
+          <t>98.2126</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3772</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.1327</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.3214</t>
+          <t>0.194</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>67.81</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>7.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>52.28</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>30.87</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.1767</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>42.99</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>0.3814</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.1492</t>
+          <t>0.1297</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3339,24 +3327,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>801126</t>
+          <t>665161</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brock Rodden</t>
+          <t>Jeremy Peña</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -3369,17 +3357,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -3388,7 +3376,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>45.6</v>
+        <v>46.1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3402,26 +3390,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>57.3</v>
+        <v>29.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>21.2</v>
+        <v>41.2</v>
       </c>
       <c r="R10" t="n">
         <v>56.1</v>
       </c>
       <c r="S10" t="n">
-        <v>40.2</v>
+        <v>93.2</v>
       </c>
       <c r="T10" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>19.5</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="n">
         <v>50</v>
@@ -3429,42 +3417,38 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr"/>
@@ -3476,17 +3460,17 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -3496,112 +3480,112 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Last 2 games: 2/8, 0 HR</t>
+          <t>Last 7 games: 4/31, 0 HR</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>88.48</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>98.2126</t>
+          <t>99.8917</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.4222</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.1438</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>0.3333</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>72.23</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.27</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>45.92</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.1793</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>42.99</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.3814</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>0.1297</t>
+          <t>0.1492</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -3657,24 +3641,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>702284</t>
+          <t>670623</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cole Young</t>
+          <t>Isaac Paredes</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -3687,17 +3671,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -3706,7 +3690,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>44.9</v>
+        <v>45.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3720,26 +3704,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>24.9</v>
+        <v>18.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>22.3</v>
+        <v>41.2</v>
       </c>
       <c r="R11" t="n">
         <v>56.1</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>37.8</v>
+        <v>53.9</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -3747,39 +3731,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3799,7 +3779,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3814,12 +3794,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/28, 1 HR</t>
+          <t>Contact streak: 10/28 over last 7 games</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -3829,97 +3809,97 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>36.63</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>88.51</t>
+          <t>86.49</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>99.0446</t>
+          <t>96.9468</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3935</t>
+          <t>0.3772</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1345</t>
+          <t>0.1327</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.3166</t>
+          <t>0.3214</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>71.51</t>
+          <t>67.81</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>21.44</t>
+          <t>7.64</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>41.63</t>
+          <t>52.28</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>27.22</t>
+          <t>30.87</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.1297</t>
+          <t>0.1767</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>42.99</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.3814</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.1297</t>
+          <t>0.1492</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -3975,12 +3955,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>663728</t>
+          <t>647304</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cal Raleigh</t>
+          <t>Josh Naylor</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4005,7 +3985,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -4024,7 +4004,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>44.7</v>
+        <v>45.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4038,26 +4018,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>54</v>
+        <v>24.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>21.2</v>
+        <v>22.3</v>
       </c>
       <c r="R12" t="n">
         <v>56.1</v>
       </c>
       <c r="S12" t="n">
-        <v>47.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>78.7</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -4065,39 +4045,35 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4117,97 +4093,97 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/23, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>89.69</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>100.7149</t>
+          <t>99.1945</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.4161</t>
+          <t>0.4068</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.2236</t>
+          <t>0.1345</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3257</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>75.06</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>52.46</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>53.38</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.1971</t>
+          <t>0.1257</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -4293,24 +4269,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>647304</t>
+          <t>514888</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Josh Naylor</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -4323,17 +4299,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -4342,7 +4318,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>43.5</v>
+        <v>42.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4356,26 +4332,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>24.7</v>
+        <v>14.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>22.3</v>
+        <v>41.2</v>
       </c>
       <c r="R13" t="n">
         <v>56.1</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>78.7</v>
+        <v>21.1</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -4383,39 +4359,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4435,27 +4407,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/23, 0 HR</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -4465,97 +4437,97 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>85.24</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>99.1945</t>
+          <t>96.9722</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.4068</t>
+          <t>0.3483</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.1345</t>
+          <t>0.1197</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.2839</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>69.07</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>22.02</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.1257</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>42.99</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.3814</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>0.1297</t>
+          <t>0.1492</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4611,24 +4583,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>514888</t>
+          <t>702284</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>Cole Young</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -4641,17 +4613,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4660,7 +4632,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>42.6</v>
+        <v>42.2</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4674,26 +4646,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>14.3</v>
+        <v>24.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.2</v>
+        <v>22.3</v>
       </c>
       <c r="R14" t="n">
         <v>56.1</v>
       </c>
       <c r="S14" t="n">
-        <v>94.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>21.1</v>
+        <v>37.8</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -4711,7 +4683,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -4749,27 +4721,27 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 0 HR</t>
+          <t>Last 7 games: 7/28, 1 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -4779,97 +4751,97 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>36.63</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>85.24</t>
+          <t>88.51</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>96.9722</t>
+          <t>99.0446</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3483</t>
+          <t>0.3935</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.1197</t>
+          <t>0.1345</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.2839</t>
+          <t>0.3166</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>69.07</t>
+          <t>71.51</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>21.44</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>41.63</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>27.22</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1297</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>42.99</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>0.3814</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>0.1492</t>
+          <t>0.1297</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4925,12 +4897,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>621493</t>
+          <t>680977</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Taylor Ward</t>
+          <t>Brendan Donovan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4974,7 +4946,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>42.3</v>
+        <v>40.9</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4988,11 +4960,11 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>32.2</v>
+        <v>15.9</v>
       </c>
       <c r="Q15" t="n">
         <v>22.3</v>
@@ -5001,13 +4973,13 @@
         <v>56.1</v>
       </c>
       <c r="S15" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>7.9</v>
+        <v>20.9</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -5015,39 +4987,35 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5067,12 +5035,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -5082,12 +5050,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/29, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -5097,67 +5065,67 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>31.87</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>89.26</t>
+          <t>86.62</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>99.4443</t>
+          <t>97.0553</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3975</t>
+          <t>0.3741</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.1546</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.3379</t>
+          <t>0.3194</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>68.67</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>22.79</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -5871,12 +5839,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>680977</t>
+          <t>642215</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brendan Donovan</t>
+          <t>Weston Wilson</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5901,7 +5869,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5920,7 +5888,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>36.2</v>
+        <v>35.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5934,11 +5902,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>15.9</v>
+        <v>24.1</v>
       </c>
       <c r="Q18" t="n">
         <v>22.3</v>
@@ -5947,13 +5915,13 @@
         <v>56.1</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>20.9</v>
+        <v>18.3</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -5961,39 +5929,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6013,27 +5977,27 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 2/17, 1 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -6043,67 +6007,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>31.87</t>
+          <t>34.91</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>86.62</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>97.0553</t>
+          <t>98.4627</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3741</t>
+          <t>0.3311</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1298</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.3194</t>
+          <t>0.281</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>68.67</t>
+          <t>72.64</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>26.54</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>47.34</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>22.79</t>
+          <t>27.46</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.1584</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -7253,7 +7217,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -7272,7 +7236,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>54.7</v>
+        <v>55.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -7286,7 +7250,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -7299,7 +7263,7 @@
         <v>56.1</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -7313,39 +7277,35 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7855,24 +7815,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>572233</t>
+          <t>677594</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Julio Rodríguez</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -7885,17 +7845,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -7918,26 +7878,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>42.7</v>
+        <v>46.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>41.2</v>
+        <v>22.3</v>
       </c>
       <c r="R5" t="n">
         <v>56.1</v>
       </c>
       <c r="S5" t="n">
-        <v>76.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>21.8</v>
+        <v>34.9</v>
       </c>
       <c r="V5" t="n">
         <v>50</v>
@@ -7955,7 +7915,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -7993,12 +7953,12 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -8008,12 +7968,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 1 HR</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -8023,97 +7983,97 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>43.09</t>
+          <t>44.43</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>90.47</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>101.5695</t>
+          <t>102.6546</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4056</t>
+          <t>0.4692</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.1757</t>
+          <t>0.195</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.3098</t>
+          <t>0.3482</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>74.31</t>
+          <t>76.61</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>43.41</t>
+          <t>67.06</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>38.56</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>26.26</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.2054</t>
+          <t>0.179</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>42.99</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.3814</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.1492</t>
+          <t>0.1297</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -8169,24 +8129,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>668227</t>
+          <t>572233</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Randy Arozarena</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -8199,17 +8159,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -8218,7 +8178,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>47</v>
+        <v>48.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8232,26 +8192,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>39.7</v>
+        <v>42.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>22.3</v>
+        <v>41.2</v>
       </c>
       <c r="R6" t="n">
         <v>56.1</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>45.5</v>
+        <v>21.8</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -8259,39 +8219,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8311,27 +8267,27 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/21, 1 HR</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -8341,97 +8297,97 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>45.49</t>
+          <t>43.09</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>91.09</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>101.0625</t>
+          <t>101.5695</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>0.4056</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1655</t>
+          <t>0.1757</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3403</t>
+          <t>0.3098</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>71.32</t>
+          <t>74.31</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>24.66</t>
+          <t>43.41</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>33.07</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1789</t>
+          <t>0.2054</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>42.99</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.3814</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.1297</t>
+          <t>0.1492</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -8487,12 +8443,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>677594</t>
+          <t>668227</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Julio Rodriguez</t>
+          <t>Randy Arozarena</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -8517,7 +8473,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8536,7 +8492,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>47</v>
+        <v>48.1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8550,11 +8506,11 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>46.1</v>
+        <v>39.7</v>
       </c>
       <c r="Q7" t="n">
         <v>22.3</v>
@@ -8563,13 +8519,13 @@
         <v>56.1</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>34.9</v>
+        <v>45.5</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -8577,39 +8533,35 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8629,22 +8581,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -8659,67 +8611,67 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>44.43</t>
+          <t>45.49</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>90.47</t>
+          <t>91.09</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>102.6546</t>
+          <t>101.0625</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.4692</t>
+          <t>0.417</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>0.1655</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3482</t>
+          <t>0.3403</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>76.61</t>
+          <t>71.32</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>67.06</t>
+          <t>24.66</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>38.56</t>
+          <t>33.07</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>26.26</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>0.1789</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -8805,24 +8757,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>665161</t>
+          <t>663728</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jeremy Peña</t>
+          <t>Cal Raleigh</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -8835,17 +8787,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -8854,7 +8806,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>46.1</v>
+        <v>47</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -8868,26 +8820,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>29.3</v>
+        <v>54</v>
       </c>
       <c r="Q8" t="n">
-        <v>41.2</v>
+        <v>21.2</v>
       </c>
       <c r="R8" t="n">
         <v>56.1</v>
       </c>
       <c r="S8" t="n">
-        <v>93.2</v>
+        <v>64.3</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -8905,7 +8857,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -8943,12 +8895,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -8958,112 +8910,112 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/31, 0 HR</t>
+          <t>Last 7 games: 2/23, 0 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>88.48</t>
+          <t>89.69</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>99.8917</t>
+          <t>100.7149</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4222</t>
+          <t>0.4161</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1438</t>
+          <t>0.2236</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3333</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>72.23</t>
+          <t>75.06</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>14.27</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>53.38</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1793</t>
+          <t>0.1971</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>42.99</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.3814</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.1492</t>
+          <t>0.1297</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -9119,24 +9071,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>670623</t>
+          <t>801126</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Isaac Paredes</t>
+          <t>Brock Rodden</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -9149,17 +9101,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -9168,7 +9120,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>45.8</v>
+        <v>46.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -9182,26 +9134,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>18.7</v>
+        <v>57.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>41.2</v>
+        <v>21.2</v>
       </c>
       <c r="R9" t="n">
         <v>56.1</v>
       </c>
       <c r="S9" t="n">
-        <v>96.59999999999999</v>
+        <v>44.8</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U9" t="n">
-        <v>53.9</v>
+        <v>19.5</v>
       </c>
       <c r="V9" t="n">
         <v>50</v>
@@ -9219,7 +9171,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -9240,7 +9192,7 @@
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr"/>
@@ -9252,132 +9204,132 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Contact streak: 10/28 over last 7 games</t>
+          <t>Last 2 games: 2/8, 0 HR</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>86.49</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>96.9468</t>
+          <t>98.2126</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3772</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.1327</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.3214</t>
+          <t>0.194</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>67.81</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>7.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>52.28</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>30.87</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.1767</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>42.99</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>0.3814</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.1492</t>
+          <t>0.1297</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -9433,24 +9385,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>801126</t>
+          <t>665161</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brock Rodden</t>
+          <t>Jeremy Peña</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -9463,17 +9415,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -9482,7 +9434,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>45.6</v>
+        <v>46.1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9496,26 +9448,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>57.3</v>
+        <v>29.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>21.2</v>
+        <v>41.2</v>
       </c>
       <c r="R10" t="n">
         <v>56.1</v>
       </c>
       <c r="S10" t="n">
-        <v>40.2</v>
+        <v>93.2</v>
       </c>
       <c r="T10" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>19.5</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="n">
         <v>50</v>
@@ -9523,42 +9475,38 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr"/>
@@ -9570,17 +9518,17 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -9590,112 +9538,112 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Last 2 games: 2/8, 0 HR</t>
+          <t>Last 7 games: 4/31, 0 HR</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>88.48</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>98.2126</t>
+          <t>99.8917</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.4222</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.1438</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>0.3333</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>72.23</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.27</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>45.92</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.1793</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>42.99</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.3814</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>0.1297</t>
+          <t>0.1492</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -9751,24 +9699,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>702284</t>
+          <t>670623</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cole Young</t>
+          <t>Isaac Paredes</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -9781,17 +9729,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -9800,7 +9748,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>44.9</v>
+        <v>45.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9814,26 +9762,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>24.9</v>
+        <v>18.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>22.3</v>
+        <v>41.2</v>
       </c>
       <c r="R11" t="n">
         <v>56.1</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>37.8</v>
+        <v>53.9</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -9841,39 +9789,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9893,7 +9837,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -9908,12 +9852,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/28, 1 HR</t>
+          <t>Contact streak: 10/28 over last 7 games</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -9923,97 +9867,97 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>36.63</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>88.51</t>
+          <t>86.49</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>99.0446</t>
+          <t>96.9468</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3935</t>
+          <t>0.3772</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1345</t>
+          <t>0.1327</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.3166</t>
+          <t>0.3214</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>71.51</t>
+          <t>67.81</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>21.44</t>
+          <t>7.64</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>41.63</t>
+          <t>52.28</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>27.22</t>
+          <t>30.87</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.1297</t>
+          <t>0.1767</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>42.99</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.3814</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.1297</t>
+          <t>0.1492</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -10069,12 +10013,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>663728</t>
+          <t>647304</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cal Raleigh</t>
+          <t>Josh Naylor</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -10099,7 +10043,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -10118,7 +10062,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>44.7</v>
+        <v>45.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -10132,26 +10076,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>54</v>
+        <v>24.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>21.2</v>
+        <v>22.3</v>
       </c>
       <c r="R12" t="n">
         <v>56.1</v>
       </c>
       <c r="S12" t="n">
-        <v>47.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>78.7</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -10159,39 +10103,35 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10211,97 +10151,97 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/23, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>89.69</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>100.7149</t>
+          <t>99.1945</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.4161</t>
+          <t>0.4068</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.2236</t>
+          <t>0.1345</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3257</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>75.06</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>52.46</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>53.38</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.1971</t>
+          <t>0.1257</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -10387,24 +10327,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>647304</t>
+          <t>514888</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Josh Naylor</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -10417,17 +10357,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -10436,7 +10376,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>43.5</v>
+        <v>42.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10450,26 +10390,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>24.7</v>
+        <v>14.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>22.3</v>
+        <v>41.2</v>
       </c>
       <c r="R13" t="n">
         <v>56.1</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>78.7</v>
+        <v>21.1</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -10477,39 +10417,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10529,27 +10465,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/23, 0 HR</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -10559,97 +10495,97 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>85.24</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>99.1945</t>
+          <t>96.9722</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.4068</t>
+          <t>0.3483</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.1345</t>
+          <t>0.1197</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.2839</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>69.07</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>22.02</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.1257</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>42.99</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.3814</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>0.1297</t>
+          <t>0.1492</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -10705,24 +10641,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>514888</t>
+          <t>702284</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>Cole Young</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -10735,17 +10671,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -10754,7 +10690,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>42.6</v>
+        <v>42.2</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10768,26 +10704,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>14.3</v>
+        <v>24.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.2</v>
+        <v>22.3</v>
       </c>
       <c r="R14" t="n">
         <v>56.1</v>
       </c>
       <c r="S14" t="n">
-        <v>94.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>21.1</v>
+        <v>37.8</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -10805,7 +10741,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -10843,27 +10779,27 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 0 HR</t>
+          <t>Last 7 games: 7/28, 1 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -10873,97 +10809,97 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>36.63</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>85.24</t>
+          <t>88.51</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>96.9722</t>
+          <t>99.0446</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3483</t>
+          <t>0.3935</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.1197</t>
+          <t>0.1345</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.2839</t>
+          <t>0.3166</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>69.07</t>
+          <t>71.51</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>21.44</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>41.63</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>27.22</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1297</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>42.99</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>0.3814</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>0.1492</t>
+          <t>0.1297</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -11019,12 +10955,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>621493</t>
+          <t>680977</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Taylor Ward</t>
+          <t>Brendan Donovan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -11068,7 +11004,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>42.3</v>
+        <v>40.9</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11082,11 +11018,11 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>32.2</v>
+        <v>15.9</v>
       </c>
       <c r="Q15" t="n">
         <v>22.3</v>
@@ -11095,13 +11031,13 @@
         <v>56.1</v>
       </c>
       <c r="S15" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>7.9</v>
+        <v>20.9</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -11109,39 +11045,35 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11161,12 +11093,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -11176,12 +11108,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/29, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -11191,67 +11123,67 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>31.87</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>89.26</t>
+          <t>86.62</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>99.4443</t>
+          <t>97.0553</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3975</t>
+          <t>0.3741</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.1546</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.3379</t>
+          <t>0.3194</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>68.67</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>22.79</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -11965,12 +11897,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>680977</t>
+          <t>642215</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brendan Donovan</t>
+          <t>Weston Wilson</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -11995,7 +11927,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -12014,7 +11946,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>36.2</v>
+        <v>35.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -12028,11 +11960,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>15.9</v>
+        <v>24.1</v>
       </c>
       <c r="Q18" t="n">
         <v>22.3</v>
@@ -12041,13 +11973,13 @@
         <v>56.1</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>20.9</v>
+        <v>18.3</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -12055,39 +11987,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12107,27 +12035,27 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 2/17, 1 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -12137,67 +12065,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>31.87</t>
+          <t>34.91</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>86.62</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>97.0553</t>
+          <t>98.4627</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3741</t>
+          <t>0.3311</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1298</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.3194</t>
+          <t>0.281</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>68.67</t>
+          <t>72.64</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>26.54</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>47.34</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>22.79</t>
+          <t>27.46</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.1584</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-08-16.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-16.xlsx
@@ -840,7 +840,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -9724,7 +9724,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -11608,7 +11608,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -12236,7 +12236,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
